--- a/backend/outputs/processed_Sales Data.xlsx
+++ b/backend/outputs/processed_Sales Data.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Visualizations" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -149,6 +150,214 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Top 10 Values by Revenue</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Visualizations'!$A$3:$A$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Visualizations'!$B$3:$B$12</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Values</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Total Annual Revenue</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Revenue Share by Attribute</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <pieChart>
+        <varyColors val="1"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Visualizations'!$A$17:$A$22</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Visualizations'!$B$17:$B$22</f>
+            </numRef>
+          </val>
+        </ser>
+        <firstSliceAng val="0"/>
+      </pieChart>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7200000" cy="3600000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>14</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4320000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1005,4 +1214,222 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Top 10 Values by Total Annual Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1795352</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SW (Customer Managed)</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1533275</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1392485</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Virtual Processor Core</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1392485</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1365495</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1358924</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1303071</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1271198</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Subscription</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>965629</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Production</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>800720</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Top Attributes by Revenue Share</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Chargeable Unit</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1642110</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Deployment Method</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1642110</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>License Term</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1642110</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Monetization Model</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1642110</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Support Type</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1642110</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Sales Motion</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1642110</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Attribute</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Values</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Add-On</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Orchestrator</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
 </file>